--- a/out/Attention-mamba2_metrics.xlsx
+++ b/out/Attention-mamba2_metrics.xlsx
@@ -472,28 +472,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02444261191412806</v>
+        <v>0.02444642651826143</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1495027095079422</v>
+        <v>0.1494740545749664</v>
       </c>
       <c r="C2" t="n">
-        <v>0.11015285551548</v>
+        <v>0.1099948883056641</v>
       </c>
       <c r="D2" t="n">
-        <v>-21.18155837059021</v>
+        <v>-21.18501958847046</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5082666666666666</v>
+        <v>0.5066666666666666</v>
       </c>
       <c r="F2" t="n">
-        <v>0.487666663788921</v>
+        <v>0.4862615604829578</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4955307262569833</v>
+        <v>0.4871508379888268</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4857668125817791</v>
+        <v>0.4808651002812916</v>
       </c>
     </row>
   </sheetData>
